--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 public documentation (CDISC website, CDISC Wiki, conference papers)</t>
+          <t>SDTMIG v3.4 public documentation (CDISC website, CDISC Wiki, conference papers); SDTM CT SDTM Domain Abbreviation codelist C66734 for domains not in SDTMIG v3.4</t>
         </is>
       </c>
     </row>
@@ -586,7 +586,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Stable — changes only when a new SDTMIG version is published.</t>
+          <t>Changes when a new SDTMIG version is published, or when SDTM CT brings test codes for a domain not yet listed (sdtm-findings-graph/notebooks/Scope_Check.ipynb).</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>One row per SDTMIG v3.4 domain (56 rows)</t>
+          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (67 rows)</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CT display names that do not match Domain_Name directly (6 rows)</t>
+          <t>CT display names that do not match Domain_Name directly (7 rows)</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full domain name from SDTMIG v3.4</t>
+          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Section number in SDTMIG v3.4 where the domain is specified</t>
+          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is a subject-level measurement domain (VS, EG, MK, CV) (Yes/No). EG included in flag despite deferred consumer status.</t>
+          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation</t>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Naming (label mismatch) or Subset (body-system sub-codelist)</t>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
         </is>
       </c>
     </row>
@@ -806,6 +806,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
@@ -821,7 +822,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Substring matched against codelist display name</t>
+          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
@@ -849,6 +850,7 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
@@ -908,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H58"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3192,6 +3194,386 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Auricular Findings</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Endocrine System Findings</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>GI</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Gastrointestinal System Findings</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>HM</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Hematopoietic System Findings</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Integumentary System Findings</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>NV</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Nervous System Findings</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Ophthalmic Examinations</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Device Properties</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device characteristics, not an observation of the subject: no consumer class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>DU</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Device In-Use</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device settings in use, not an observation of the subject: no consumer class.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Tobacco Product Testing</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n"/>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Tobacco product sample testing, not an observation of the subject: no consumer class.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3204,7 +3586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3364,6 +3746,24 @@
       <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Body-system subset of Disease Response and Clin Classification</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Physical Properties</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Cross-domain</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>PHSPRPCD/PHSPRP: physical characteristics of an entity (Color, Diameter, Ulceration, ...). Test codes reused across domains (e.g. DIAMETER in FA, GI, OE, SR, TR); no domain of its own in C66734.</t>
         </is>
       </c>
     </row>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelist_Overrides" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument_Domain_Rules" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer_Exclusions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Domains'!$A$1:$G$57</definedName>
@@ -469,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -640,264 +641,353 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Consumer_Exclusions</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (5 rows)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>COLUMN DESCRIPTIONS</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Two-letter SDTM domain abbreviation (RELREC/RELSPEC for relationship datasets)</t>
-        </is>
-      </c>
+      <c r="B21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Domain_Name</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
+          <t>Two-letter SDTM domain abbreviation (RELREC/RELSPEC for relationship datasets)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Observation_Class</t>
+          <t>Domain_Name</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design, Relationship</t>
+          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG_Section</t>
+          <t>Observation_Class</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
+          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design, Relationship</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Has_Test_Codes</t>
+          <t>SDTMIG_Section</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
+          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Specimen_Based</t>
+          <t>Has_Test_Codes</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is specimen-based per SDTMIG v3.4 Section 6.3.5 (Yes/No)</t>
+          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Specimen_Based</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+          <t>Whether the domain is specimen-based per SDTMIG v3.4 Section 6.3.5 (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Brief notes on domain status or version history</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-      <c r="B29" s="2" t="n"/>
-    </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>CODELIST_OVERRIDES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CT_Display_Name</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>CT_Display_Name</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
+          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Override_Type</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>Override_Type</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>Description of the mismatch</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation</t>
+          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Target SDTM domain abbreviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Description and examples of instrument types in this category</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN LIMITATIONS</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-    </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>CONSUMER_EXCLUSIONS COLUMNS</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>That requires CDISC membership access to the SDTM v2.0 Excel files.</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n"/>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SDTM v3.0 is under review and may add or change domains.</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n"/>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Domain excluded from that consumer's scope</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n"/>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Identifier of one testable claim behind the exclusion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>The exclusion reason as recorded in the consumer notebook</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>KNOWN LIMITATIONS</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>That requires CDISC membership access to the SDTM v2.0 Excel files.</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SDTM v3.0 is under review and may add or change domains.</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
           <t>SDTMIG section numbers are reconstructed from public sources — verify against the IG.</t>
         </is>
       </c>
-      <c r="B46" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3859,4 +3949,218 @@
   <autoFilter ref="A1:C4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Specimen_Findings</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>IS-1</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Every BC that fans out differs by binding agent</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>axis_all:binding agent</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Target-driven, not specimen-driven: the DSSs of one BC differ by binding agent (BDAGNT), the target. The March 2026 analysis found the target only in the DS code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Specimen_Findings</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>IS-2</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Specimen is not the primary axis</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>not_primary:specimen</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Target-driven, not specimen-driven: the DSSs of one BC differ by binding agent (BDAGNT), the target. The March 2026 analysis found the target only in the DS code.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Specimen_Findings</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>GF-1</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Every BC that fans out differs by test detail</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>axis_all:test detail</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Test-detail-driven, not specimen-driven: the DSSs of one BC differ by test detail (TSTDTL). The March 2026 analysis recorded it as scale-driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Specimen_Findings</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>GF-2</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Specimen is not the primary axis</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>not_primary:specimen</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Test-detail-driven, not specimen-driven: the DSSs of one BC differ by test detail (TSTDTL). The March 2026 analysis recorded it as scale-driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Specimen_Findings</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>UR</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>UR-1</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>No BC has more than one DSS</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>no_fanout</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Zero decomposition despite Specimen_Based metadata flag.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelist_Overrides" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument_Domain_Rules" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer_Exclusions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Meaning" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Domains'!$A$1:$G$57</definedName>
@@ -470,7 +471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -593,401 +594,515 @@
       <c r="B13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Variable_Meaning is the exception: our position, not a published fact, with the basis stated per row.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>SHEETS</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Domains</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (67 rows)</t>
-        </is>
-      </c>
+      <c r="B16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Codelist_Overrides</t>
+          <t>Domains</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CT display names that do not match Domain_Name directly (7 rows)</t>
+          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (67 rows)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Instrument_Domain_Rules</t>
+          <t>Codelist_Overrides</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Keyword-to-domain mapping for non-extensible instrument codelists (3 rows)</t>
+          <t>CT display names that do not match Domain_Name directly (7 rows)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Instrument_Domain_Rules</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Keyword-to-domain mapping for non-extensible instrument codelists (3 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Consumer_Exclusions</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (5 rows)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-      <c r="B20" s="2" t="n"/>
-    </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Variable_Meaning</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (22 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>COLUMN DESCRIPTIONS</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Two-letter SDTM domain abbreviation (RELREC/RELSPEC for relationship datasets)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Domain_Name</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
-        </is>
-      </c>
+      <c r="B23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Observation_Class</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design, Relationship</t>
+          <t>Two-letter SDTM domain abbreviation (RELREC/RELSPEC for relationship datasets)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG_Section</t>
+          <t>Domain_Name</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
+          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Has_Test_Codes</t>
+          <t>Observation_Class</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
+          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design, Relationship</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Specimen_Based</t>
+          <t>SDTMIG_Section</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is specimen-based per SDTMIG v3.4 Section 6.3.5 (Yes/No)</t>
+          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Has_Test_Codes</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>Specimen_Based</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain is specimen-based per SDTMIG v3.4 Section 6.3.5 (Yes/No)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Brief notes on domain status or version history</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
-      <c r="B30" s="2" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>CODELIST_OVERRIDES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CT_Display_Name</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Override_Type</t>
+          <t>CT_Display_Name</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Override_Type</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>Description of the mismatch</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Target SDTM domain abbreviation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>Keyword</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Target SDTM domain abbreviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Description and examples of instrument types in this category</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>CONSUMER_EXCLUSIONS COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Domain excluded from that consumer's scope</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Claim_ID</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Identifier of one testable claim behind the exclusion</t>
+          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+          <t>Domain excluded from that consumer's scope</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Claim_ID</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+          <t>Identifier of one testable claim behind the exclusion</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>The exclusion reason as recorded in the consumer notebook</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>VARIABLE_MEANING COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Key_Source</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>The variable, or the axis for Key_Compare rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>The part of the observable key it identifies: component, system, method, scale; or open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Basis_Note</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>What each source states, by sheet and column; the rule, where one is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>proposed / accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>KNOWN LIMITATIONS</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="B61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
         </is>
       </c>
-      <c r="B51" s="2" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="B62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>That requires CDISC membership access to the SDTM v2.0 Excel files.</t>
         </is>
       </c>
-      <c r="B52" s="2" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="B63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>SDTM v3.0 is under review and may add or change domains.</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>SDTMIG section numbers are reconstructed from public sources — verify against the IG.</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4163,4 +4278,874 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="110" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Key_Source</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Basis_Note</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LBSPEC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GFSPEC</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist GENSMP. Fan-out axis specimen and key part system agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ISSPEC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LBMETHOD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare).</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GFMETHOD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ISMETHOD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GFTSTDTL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ISTSTDTL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MBTSTDTL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare).</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MITSTDTL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>COSMoS only: as MBTSTDTL, codelist MIFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MI.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ISBDAGNT</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sources agree</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>COSMoS only: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LBTESTCD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sources disagree, decided by a stated rule</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>COSMoS puts GLUC and GLUCPE under one BC (C105585). SDTM CT publishes them as separate LBTESTCD terms with their own NCIt codes and definitions (GLUC C105585; GLUCPE C163446, "plasma equivalent glucose"). The key separates them; the fan-out does not. Rule (adopted 2026-10-08): a separate SDTM CT test term with its own NCIt code is a separate component (identity keyed on NCIt codes, Observables_Direction step 2).</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Key_Compare</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sources disagree, decided by a stated rule</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rule (decided 2026-10-06): result scale is treated as distinguishing an observable, on the standards' own grounds: DSSs of one BC differ by scale, and LOINC has scale as an axis. No claim that it is clinically right. Disagreement: the fan-out reads units present or absent; the key reads the --ORRES data type (Key_Compare). COSMoS publishes result scale per BC, not per DSS (Scale_Units). The rule does not settle which per-DSS reading is right.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GFANMETH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LBCAT</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RSCAT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GFSYMTYP</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate IS_POSITION_FOR, "is the type of genomic entity that is the position of the result in", codelist SYMTYPGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GF</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GFINHERT</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate IS_ATTRIBUTE_FOR, "indicates heritability of the genetic variant in", codelist INHERTGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TRGRPID</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>COSMoS: no predicate, no linking phrase; DEC Tumor Results Group Identifier. No codelist; values without NCIt code. Besides the DS code, the only assigned value that separates TR DSSs. No source says whether it changes the observation.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VSPOS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Rater_COSMoS_EVAL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>QSEVAL</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Rater_COSMoS_EVAL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>RSEVAL</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -839,7 +839,6 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
@@ -883,7 +882,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
@@ -963,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
@@ -1055,7 +1052,6 @@
         </is>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
@@ -4368,7 +4364,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4401,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4438,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4475,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4512,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4549,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4586,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4618,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. Held 2026-10-08: DEC label not stated on all DSSs.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4664,7 +4660,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4697,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4734,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4775,7 +4771,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4781,6 @@
           <t>Key_Compare</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>scale</t>
@@ -4808,7 +4803,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4840,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4877,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4914,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4951,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4988,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5025,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5057,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable.</t>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. Held 2026-10-08: LOINC has position-free and position-qualified codes side by side; to be backed by a cell before the row is accepted.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5104,7 +5099,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5136,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (22 rows)</t>
+          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (23 rows)</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name)</t>
+          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The part of the observable key it identifies: component, system, method, scale; or open</t>
+          <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>That requires CDISC membership access to the SDTM v2.0 Excel files.</t>
+          <t>CDISC publishes it as the SDTM v2.0 and SDTMIG v3.4 variable tables (sign-in at cdisc.org). Local copies sit in sdtm-domain-reference/downloads/ (gitignored); domain-behaviour reads them.</t>
         </is>
       </c>
       <c r="B63" s="2" t="n"/>
@@ -4282,7 +4282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check.</t>
+          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist GENSMP. Fan-out axis specimen and key part system agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist GENSMP. Fan-out axis specimen and key part system agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare).</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. Held 2026-10-08: DEC label not stated on all DSSs.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. Held 2026-10-08 for the DEC label; resolved: SDTM v2.0 and SDTMIG v3.4 both give Variable Qualifier of --TESTCD.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare).</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sources agree</t>
+          <t>sources disagree, decided by a stated rule</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS only: as MBTSTDTL, codelist MIFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MI.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier. Rule, for now: the Model's Variables Qualified and the sibling --TSTDTL rows hold over the IG role.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>proposed</t>
         </is>
       </c>
     </row>
@@ -4729,7 +4729,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COSMoS puts GLUC and GLUCPE under one BC (C105585). SDTM CT publishes them as separate LBTESTCD terms with their own NCIt codes and definitions (GLUC C105585; GLUCPE C163446, "plasma equivalent glucose"). The key separates them; the fan-out does not. Rule (adopted 2026-10-08): a separate SDTM CT test term with its own NCIt code is a separate component (identity keyed on NCIt codes, Observables_Direction step 2).</t>
+          <t>COSMoS puts GLUC and GLUCPE under one BC (C105585). SDTM CT publishes them as separate LBTESTCD terms with their own NCIt codes and definitions (GLUC C105585; GLUCPE C163446, "plasma equivalent glucose"). The key separates them; the fan-out does not. Rule (adopted 2026-10-08): a separate SDTM CT test term with its own NCIt code is a separate component (identity keyed on NCIt codes, Observables_Direction step 2). SDTM v2.0 and SDTMIG v3.4: Topic.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_POSITION_FOR, "is the type of genomic entity that is the position of the result in", codelist SYMTYPGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation.</t>
+          <t>COSMoS: predicate IS_POSITION_FOR, "is the type of genomic entity that is the position of the result in", codelist SYMTYPGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --SYM (the gene symbol).</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not part of the observable</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>standards silent, open</t>
+          <t>sources agree</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_ATTRIBUTE_FOR, "indicates heritability of the genetic variant in", codelist INHERTGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation.</t>
+          <t>COSMoS: IS_ATTRIBUTE_FOR, "indicates heritability of the genetic variant in", codelist INHERTGF. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --ORRES, --STRESC, --STRESN. Both say it qualifies the result, not the test.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5010,22 +5010,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not part of the observable</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>standards silent, open</t>
+          <t>sources agree</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>COSMoS: no predicate, no linking phrase; DEC Tumor Results Group Identifier. No codelist; values without NCIt code. Besides the DS code, the only assigned value that separates TR DSSs. No source says whether it changes the observation.</t>
+          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>proposed</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. Held 2026-10-08: LOINC has position-free and position-qualified codes side by side; to be backed by a cell before the row is accepted.</t>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -5135,6 +5135,43 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LOINC_Subject_State</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LBFAST</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>accepted</t>
         </is>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions): 'GFMETHOD lists wet lab techniques …; methods related to specimen processing or reagents are not represented in GFMETHOD.'</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 MB Assumption 1 (IG_Assumptions): 'DETECTION' for tests that identify an organism; for a characteristic, 'the name of the characteristic being described (e.g., COLONY COUNT, VIRAL LOAD)'.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier. Rule, for now: the Model's Variables Qualified and the sibling --TSTDTL rows hold over the IG role.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier. Rule, for now: the Model's Variables Qualified and the sibling --TSTDTL rows hold over the IG role. SDTMIG v3.4 MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own Record Qualifier role.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4835,7 +4835,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions) confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing).</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts.</t>
+          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts. SDTMIG v3.4 TR Assumptions 1 and 2 (IG_Assumptions): --GRPID 'may be used for other purposes, per the SDTM', so TR/TU links use --LNKID/--LNKGRP instead.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers.</t>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. The SDTMIG v3.4 VS Assumptions do not discuss VSPOS; LB Assumption 8 (IG_Assumptions) names LBPOS (in LB) among the LOINC-associated aspects of a test.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property.</t>
+          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7 (IG_Assumptions): RSEVALID with RSEVAL gives detail of who provides the assessment.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers.</t>
+          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2).</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -4692,12 +4692,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier. Rule, for now: the Model's Variables Qualified and the sibling --TSTDTL rows hold over the IG role. SDTMIG v3.4 MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own Record Qualifier role.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own role. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelist_Overrides" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument_Domain_Rules" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer_Exclusions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Meaning" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non_Observation_Datasets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer_Exclusions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable_Meaning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Domains'!$A$1:$G$57</definedName>
@@ -471,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -505,7 +506,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG v3.4 public documentation (CDISC website, CDISC Wiki, conference papers); SDTM CT SDTM Domain Abbreviation codelist C66734 for domains not in SDTMIG v3.4</t>
+          <t>SDTMIG v3.4 variable table and table of contents (downloaded with a cdisc.org sign-in; checked 2026-10-12); SDTM CT SDTM Domain Abbreviation codelist C66734 for domains not in SDTMIG v3.4</t>
         </is>
       </c>
     </row>
@@ -580,7 +581,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Contains factual properties of SDTM domains sourced from public SDTMIG documentation.</t>
+          <t>Contains factual properties of SDTM domains from SDTMIG v3.4 and SDTM CT.</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -620,7 +621,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (67 rows)</t>
+          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (66 rows)</t>
         </is>
       </c>
     </row>
@@ -651,454 +652,565 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Non_Observation_Datasets</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 datasets that are not domains of observations, each with the reason (5 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Consumer_Exclusions</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (5 rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (4 rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Variable_Meaning</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (23 rows)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="n"/>
-    </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>COLUMN DESCRIPTIONS</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Two-letter SDTM domain abbreviation (RELREC/RELSPEC for relationship datasets)</t>
-        </is>
-      </c>
+      <c r="B24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Domain_Name</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Full domain name from SDTMIG v3.4; for domains added from CT, the C66734 name</t>
+          <t>Two-letter SDTM domain abbreviation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Observation_Class</t>
+          <t>Domain_Name</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design, Relationship</t>
+          <t>Domain name used to match SDTM CT codelist names (sdtm-test-codes/notebooks/SDTM_CT_Extract.ipynb); the SDTMIG v3.4 name for most domains, the C66734 name for domains added from CT. IG_Name has the IG name.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG_Section</t>
+          <t>Observation_Class</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Section number in SDTMIG v3.4 where the domain is specified (empty for domains added from CT)</t>
+          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design. FA and SR are Findings here (the consumers filter on it); IG_Class has Findings About.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Has_Test_Codes</t>
+          <t>SDTMIG_Section</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
+          <t>Section number in the SDTMIG v3.4 table of contents (empty for domains added from CT). MB, MS (6.3.5.7) and PC, PP (6.3.5.9) are listed only under a group heading.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Specimen_Based</t>
+          <t>Has_Test_Codes</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is specimen-based per SDTMIG v3.4 Section 6.3.5 (Yes/No)</t>
+          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Specimen_Based</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+          <t>Whether the domain is specimen-based: listed under SDTMIG v3.4 Section 6.3.5 Specimen-based Findings Domains (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Measurement</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Brief notes on domain status or version history</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-      <c r="B32" s="2" t="n"/>
-    </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>CODELIST_OVERRIDES COLUMNS</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>IG_Name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Domain name in the SDTMIG v3.4 table of contents (the sheet name for MB, MS, PC, PP); empty for domains added from CT</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CT_Display_Name</t>
+          <t>IG_Class</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
+          <t>Class in the SDTMIG v3.4 variable table; empty for domains added from CT</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Override_Type</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>CODELIST_OVERRIDES COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>CT_Display_Name</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Description of the mismatch</t>
+          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Override_Type</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Description of the mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Keyword</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>Target SDTM domain abbreviation</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Description and examples of instrument types in this category</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>CONSUMER_EXCLUSIONS COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Domain excluded from that consumer's scope</t>
-        </is>
-      </c>
-    </row>
+          <t>Description and examples of instrument types in this category</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Claim_ID</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Identifier of one testable claim behind the exclusion</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>NON_OBSERVATION_DATASETS COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+          <t>SDTMIG v3.4 dataset name</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>IG_Name</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+          <t>Name in the SDTMIG v3.4 table of contents (8.4.1 Supplemental Qualifiers (SUPP--) for SUPPQUAL)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>IG_Class</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Class in the SDTMIG v3.4 variable table</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG_Section</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Section number in the SDTMIG v3.4 table of contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Why the dataset is not listed in Domains</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>CONSUMER_EXCLUSIONS COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Domain excluded from that consumer's scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Identifier of one testable claim behind the exclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>The exclusion reason as recorded in the consumer notebook</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>VARIABLE_MEANING COLUMNS</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Key_Source</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Key</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>The variable, or the axis for Key_Compare rows</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Basis_Note</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>What each source states, by sheet and column; the rule, where one is used</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>proposed / accepted</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>KNOWN LIMITATIONS</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="B71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
         </is>
       </c>
-      <c r="B62" s="2" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="B72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>CDISC publishes it as the SDTM v2.0 and SDTMIG v3.4 variable tables (sign-in at cdisc.org). Local copies sit in sdtm-domain-reference/downloads/ (gitignored); domain-behaviour reads them.</t>
         </is>
       </c>
-      <c r="B63" s="2" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="B73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>SDTM v3.0 is under review and may add or change domains.</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="B74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
         </is>
       </c>
-      <c r="B65" s="2" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG section numbers are reconstructed from public sources — verify against the IG.</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG_Section, IG_Name, IG_Class, Has_Test_Codes and Specimen_Based, and the Non_Observation_Datasets sheet, are checked against SDTMIG v3.4 by sdtm-findings-graph/notebooks/Scope_Check.ipynb (section 5).</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1111,7 +1223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1233,8 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1164,6 +1278,16 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>IG_Name</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>IG_Class</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1202,6 +1326,16 @@
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Special-Purpose</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1240,6 +1374,16 @@
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Demographics</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>Special-Purpose</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1278,6 +1422,16 @@
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Subject Elements</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Special-Purpose</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1316,6 +1470,16 @@
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Subject Disease Milestones</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Special-Purpose</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1354,6 +1518,16 @@
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Subject Visits</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>Special-Purpose</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1392,6 +1566,16 @@
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Procedure Agents</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1430,6 +1614,16 @@
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Concomitant/Prior Medications</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1449,7 +1643,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>6.1.3</t>
+          <t>6.1.3.2</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1468,6 +1662,16 @@
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Exposure as Collected</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1487,7 +1691,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>6.1.4</t>
+          <t>6.1.3.1</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1506,6 +1710,16 @@
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1525,7 +1739,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>6.1.5</t>
+          <t>6.1.4</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1546,6 +1760,16 @@
       <c r="H11" s="5" t="inlineStr">
         <is>
           <t>New in v3.4 scope</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Meal Data</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1791,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>6.1.6</t>
+          <t>6.1.5</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1586,6 +1810,16 @@
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Procedures</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1605,7 +1839,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>6.1.7</t>
+          <t>6.1.6</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1624,6 +1858,16 @@
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Substance Use</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Interventions</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1662,6 +1906,16 @@
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Adverse Events</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1704,6 +1958,16 @@
           <t>From SDTMIG-PGx v1.0</t>
         </is>
       </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Biospecimen Events</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1742,6 +2006,16 @@
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Clinical Events</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1780,6 +2054,16 @@
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1799,7 +2083,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>6.2.5</t>
+          <t>6.2.7</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1818,6 +2102,16 @@
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Protocol Deviations</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1837,7 +2131,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>6.2.6</t>
+          <t>6.2.5</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1856,6 +2150,16 @@
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Healthcare Encounters</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1875,7 +2179,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>6.2.7</t>
+          <t>6.2.6</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1894,6 +2198,16 @@
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Medical History</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1932,6 +2246,16 @@
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Product Accountability</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1970,6 +2294,16 @@
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Death Details</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2008,6 +2342,16 @@
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>ECG Test Results</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2046,6 +2390,16 @@
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Inclusion/Exclusion Criteria Not Met</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2065,7 +2419,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.1</t>
+          <t>6.3.5.2</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2086,6 +2440,16 @@
       <c r="H25" s="5" t="inlineStr">
         <is>
           <t>From SDTMIG-PGx v1.0</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Biospecimen Findings</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2471,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.2</t>
+          <t>6.3.5.3</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2128,6 +2492,16 @@
       <c r="H26" s="5" t="inlineStr">
         <is>
           <t>New in v3.4</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Cell Phenotype Findings</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2523,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.3</t>
+          <t>6.3.5.4</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2170,6 +2544,16 @@
       <c r="H27" s="5" t="inlineStr">
         <is>
           <t>New in v3.4</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Genomics Findings</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2575,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.4</t>
+          <t>6.3.5.5</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2212,6 +2596,16 @@
       <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Scope expanded in v3.4</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Immunogenicity Specimen Assessments</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2627,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.5</t>
+          <t>6.3.5.6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2252,6 +2646,16 @@
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Laboratory Test Results</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -2271,7 +2675,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.6</t>
+          <t>6.3.5.7</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2290,6 +2694,16 @@
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Microbiology Specimen</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -2309,7 +2723,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.7</t>
+          <t>6.3.5.8</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2328,6 +2742,16 @@
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Microscopic Findings</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -2347,7 +2771,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>6.3.5.8</t>
+          <t>6.3.5.7</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2366,6 +2790,16 @@
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Microbiology Susceptibility</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -2404,6 +2838,16 @@
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacokinetics Concentrations</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -2446,6 +2890,16 @@
           <t>Paired with PC</t>
         </is>
       </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacokinetics Parameters</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -2465,7 +2919,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>6.3.6</t>
+          <t>6.4.4</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2484,6 +2938,16 @@
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Findings About Events or Interventions</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Findings About</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -2503,7 +2967,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>6.3.7</t>
+          <t>6.3.9.1</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2524,6 +2988,16 @@
       <c r="H36" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Functional Tests</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2545,7 +3019,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>6.3.8</t>
+          <t>6.3.7.3</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2564,6 +3038,16 @@
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Musculoskeletal System Findings</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2583,7 +3067,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>6.3.9</t>
+          <t>6.3.9.2</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2604,6 +3088,16 @@
       <c r="H38" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Questionnaires</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2625,7 +3119,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>6.3.10</t>
+          <t>6.3.7.6</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2644,6 +3138,16 @@
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Reproductive System Findings</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2663,7 +3167,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>6.3.11</t>
+          <t>6.3.9.3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2684,6 +3188,16 @@
       <c r="H40" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Disease Response and Clin Classification</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2705,7 +3219,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>6.3.12</t>
+          <t>6.3.10</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2724,6 +3238,16 @@
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Subject Characteristics</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2743,7 +3267,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>6.3.13</t>
+          <t>6.4.5</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2762,6 +3286,16 @@
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Skin Response</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Findings About</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2781,7 +3315,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>6.3.14</t>
+          <t>6.3.11</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2800,6 +3334,16 @@
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Subject Status</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2819,7 +3363,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>6.3.15</t>
+          <t>6.3.12.2</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2840,6 +3384,16 @@
       <c r="H44" s="5" t="inlineStr">
         <is>
           <t>Oncology</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Tumor/Lesion Results</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2861,7 +3415,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>6.3.16</t>
+          <t>6.3.12.1</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2882,6 +3436,16 @@
       <c r="H45" s="5" t="inlineStr">
         <is>
           <t>Oncology</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Tumor/Lesion Identification</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3467,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>6.3.17</t>
+          <t>6.3.7.8</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2913,7 +3477,7 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2922,6 +3486,16 @@
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Urinary System Findings</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2941,7 +3515,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>6.3.18</t>
+          <t>6.3.13</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2960,6 +3534,16 @@
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Vital Signs</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2979,7 +3563,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>6.3.19</t>
+          <t>6.3.7.2</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -3000,6 +3584,16 @@
       <c r="H48" s="5" t="inlineStr">
         <is>
           <t>TAUG-CV</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Cardiovascular System Findings</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3615,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.2.1</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3040,6 +3634,16 @@
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Trial Arms</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
@@ -3049,7 +3653,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Trial Disease Milestones</t>
+          <t>Trial Disease Assessments</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3059,7 +3663,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3.2</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3078,6 +3682,16 @@
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Trial Disease Assessments</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
@@ -3097,7 +3711,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.2.2</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3116,6 +3730,16 @@
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Trial Elements</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -3135,7 +3759,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>7.4.1</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -3154,6 +3778,16 @@
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Trial Inclusion/Exclusion Criteria</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -3173,7 +3807,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.4.2</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -3192,6 +3826,16 @@
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Trial Summary</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -3211,7 +3855,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.3.1</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -3230,31 +3874,41 @@
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Trial Visits</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>VE</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Missed Visits</t>
+          <t>Respiratory System Findings</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Trial Design</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.3.7.7</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
@@ -3264,39 +3918,45 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>New in v3.4</t>
+          <t>Body System Findings domain (introduced SDTMIG v3.3, 2018). COSMoS BC/DSS coverage added in 2026-03 package: 135 DSS, primarily pulmonary function and respiratory mechanics.</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Respiratory System Findings</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>RELREC</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Related Records</t>
+          <t>Auricular Findings</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>8.1</t>
-        </is>
-      </c>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n"/>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
@@ -3309,32 +3969,32 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr"/>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>RELSPEC</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Related Specimens</t>
+          <t>Endocrine System Findings</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Relationship</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>8.2</t>
-        </is>
-      </c>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n"/>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
@@ -3349,19 +4009,19 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>From SDTMIG-PGx v1.0</t>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>RE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Respiratory System Findings</t>
+          <t>Gastrointestinal System Findings</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -3369,11 +4029,7 @@
           <t>Findings</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>6.3.10</t>
-        </is>
-      </c>
+      <c r="D58" s="5" t="n"/>
       <c r="E58" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3386,24 +4042,24 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Body System Findings domain (introduced SDTMIG v3.3, 2018). COSMoS BC/DSS coverage added in 2026-03 package: 135 DSS, primarily pulmonary function and respiratory mechanics.</t>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>HM</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Auricular Findings</t>
+          <t>Hematopoietic System Findings</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3436,12 +4092,12 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Endocrine System Findings</t>
+          <t>Integumentary System Findings</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -3474,12 +4130,12 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Gastrointestinal System Findings</t>
+          <t>Nervous System Findings</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3487,7 +4143,11 @@
           <t>Findings</t>
         </is>
       </c>
-      <c r="D61" s="5" t="n"/>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>6.3.7.4</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3505,19 +4165,29 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+          <t>In SDTMIG v3.4 (6.3.7.4). Listed here first on 2026-10-01 from SDTM CT C66734 as a domain not in the IG; corrected 2026-10-12. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Nervous System Findings</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>HM</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Hematopoietic System Findings</t>
+          <t>Ophthalmic Examinations</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -3525,7 +4195,11 @@
           <t>Findings</t>
         </is>
       </c>
-      <c r="D62" s="5" t="n"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>6.3.7.5</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3543,19 +4217,29 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+          <t>In SDTMIG v3.4 (6.3.7.5). Listed here first on 2026-10-01 from SDTM CT C66734 as a domain not in the IG; corrected 2026-10-12. Consumer class pending published COSMoS content.</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Ophthalmic Examinations</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>DO</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Integumentary System Findings</t>
+          <t>Device Properties</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3581,19 +4265,19 @@
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device characteristics, not an observation of the subject: no consumer class.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>DU</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Nervous System Findings</t>
+          <t>Device In-Use</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -3619,19 +4303,19 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device settings in use, not an observation of the subject: no consumer class.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Ophthalmic Examinations</t>
+          <t>Tobacco Product Testing</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -3657,19 +4341,19 @@
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
+          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Tobacco product sample testing, not an observation of the subject: no consumer class.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>DO</t>
+          <t>PE</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Device Properties</t>
+          <t>Physical Examination</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -3677,7 +4361,11 @@
           <t>Findings</t>
         </is>
       </c>
-      <c r="D66" s="5" t="n"/>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>6.3.8</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -3695,30 +4383,44 @@
       </c>
       <c r="H66" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device characteristics, not an observation of the subject: no consumer class.</t>
+          <t>Added 2026-10-12 from SDTMIG v3.4.</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Physical Examination</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>Findings</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>DU</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Device In-Use</t>
+          <t>Trial Disease Milestones</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Findings</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n"/>
+          <t>Trial Design</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>7.3.3</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
@@ -3733,45 +4435,17 @@
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device settings in use, not an observation of the subject: no consumer class.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>Tobacco Product Testing</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Findings</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n"/>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Tobacco product sample testing, not an observation of the subject: no consumer class.</t>
+          <t>Added 2026-10-12 from SDTMIG v3.4.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Trial Disease Milestones</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Trial Design</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4742,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>IG_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>IG_Class</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>SDTMIG_Section</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>RELREC</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Related Records</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>8.2.1</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Relationship dataset: relates records across domains. Not a domain of observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>RELSPEC</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Related Specimens</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Relationship dataset: relates specimens to each other (parent and derived specimens). Not a domain of observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RELSUB</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Related Subjects</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Relationship dataset: relates subjects to each other. Not a domain of observations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SUPPQUAL</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Supplemental Qualifiers</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Relationship</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>8.4.1</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>SUPP-- datasets: a structure for non-standard variables, one per parent domain. Not a domain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>OI</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Non-host Organism Identifiers</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Study Reference</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Study reference dataset: reference data about non-host organisms, not observations about a subject.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4239,44 +5096,12 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Specimen_Findings</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>UR</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>UR-1</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>No BC has more than one DSS</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>no_fanout</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Zero decomposition despite Specimen_Based metadata flag.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (23 rows)</t>
+          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (26 rows)</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
+          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name), Interpretation_Context (Domain + variable, with COSMoS content); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6002,6 +6002,117 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Interpretation_Context</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>QS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>QSEVINTX</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Interpretation_Context: COSMoS_Use = always assigned in QS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Interpretation_Context</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>RSEVINTX</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Interpretation_Context</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RSEVLINT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReadMe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Domains" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codelist_Overrides" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument_Domain_Rules" sheetId="4" state="visible" r:id="rId4"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -487,13 +487,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>PROVENANCE</t>
+          <t>PURPOSE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -501,87 +501,62 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 variable table and table of contents (downloaded with a cdisc.org sign-in; checked 2026-10-12); SDTM CT SDTM Domain Abbreviation codelist C66734 for domains not in SDTMIG v3.4</t>
-        </is>
-      </c>
+          <t>Reference data for programmatic use by notebooks and other tracks.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SDTM Model</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
+          <t>Contains factual properties of SDTM domains from SDTMIG v3.4 and SDTM CT.</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>v3.4 (2021, current as of March 2026)</t>
-        </is>
-      </c>
+          <t>Changes when a new SDTMIG version is published, or when SDTM CT brings test codes for a domain not yet listed (sdtm-findings-graph/notebooks/Scope_Check.ipynb).</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Created</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Variable_Meaning is the exception: our position, not a published fact, with the basis stated per row.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/kerfors/cdisc-for-ai</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SCOPE</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>PURPOSE</t>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>All SDTMIG v3.4 domains of observations, Trial Design and Special-Purpose, plus the domains SDTM CT C66734 lists that are not in SDTMIG v3.4 (Notes say which). Datasets that are not domains of observations are in Non_Observation_Datasets.</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Reference data for programmatic use by notebooks and other tracks.</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="n"/>
       <c r="B11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Contains factual properties of SDTM domains from SDTMIG v3.4 and SDTM CT.</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>SOURCE VERSIONS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -589,110 +564,119 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Changes when a new SDTMIG version is published, or when SDTM CT brings test codes for a domain not yet listed (sdtm-findings-graph/notebooks/Scope_Check.ipynb).</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
+          <t>SDTM CT</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 (pinned in Reference_Versions.json at the repo root; written here by hand, this file has no notebook)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Variable_Meaning is the exception: our position, not a published fact, with the basis stated per row.</t>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>COSMoS</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14 (pinned; not read by this file)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="n"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 variable table and table of contents (downloaded with a cdisc.org sign-in; checked 2026-10-12); SDTM CT SDTM Domain Abbreviation codelist C66734 for domains not in SDTMIG v3.4</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SDTM Model</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>v2.0</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Domains</t>
+          <t>SDTMIG</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (66 rows)</t>
+          <t>v3.4 (2021, current as of March 2026)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Codelist_Overrides</t>
+          <t>Created</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>CT display names that do not match Domain_Name directly (7 rows)</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Instrument_Domain_Rules</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Keyword-to-domain mapping for non-extensible instrument codelists (3 rows)</t>
+          <t>https://github.com/kerfors/cdisc-for-ai</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Non_Observation_Datasets</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 datasets that are not domains of observations, each with the reason (5 rows)</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>Consumer_Exclusions</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (4 rows)</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>KNOWN GAPS</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Variable_Meaning</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (26 rows)</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CDISC publishes it as the SDTM v2.0 and SDTMIG v3.4 variable tables (sign-in at cdisc.org). Local copies sit in sdtm-domain-reference/downloads/ (gitignored); domain-behaviour reads them.</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>COLUMN DESCRIPTIONS</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SDTM v3.0 is under review and may add or change domains.</t>
         </is>
       </c>
       <c r="B24" s="2" t="n"/>
@@ -700,291 +684,291 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Two-letter SDTM domain abbreviation</t>
-        </is>
-      </c>
+          <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Domain_Name</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Domain name used to match SDTM CT codelist names (sdtm-test-codes/notebooks/SDTM_CT_Extract.ipynb); the SDTMIG v3.4 name for most domains, the C66734 name for domains added from CT. IG_Name has the IG name.</t>
-        </is>
-      </c>
+          <t>SDTMIG_Section, IG_Name, IG_Class, Has_Test_Codes and Specimen_Based, and the Non_Observation_Datasets sheet, are checked against SDTMIG v3.4 by sdtm-findings-graph/notebooks/Scope_Check.ipynb (section 5).</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Observation_Class</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design. FA and SR are Findings here (the consumers filter on it); IG_Class has Findings About.</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG_Section</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Section number in the SDTMIG v3.4 table of contents (empty for domains added from CT). MB, MS (6.3.5.7) and PC, PP (6.3.5.9) are listed only under a group heading.</t>
-        </is>
-      </c>
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>SHEETS</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Has_Test_Codes</t>
+          <t>Domains</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
+          <t>One row per SDTM domain: SDTMIG v3.4, plus domains added from SDTM CT C66734 (see Notes) (66 rows)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Specimen_Based</t>
+          <t>Codelist_Overrides</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is specimen-based: listed under SDTMIG v3.4 Section 6.3.5 Specimen-based Findings Domains (Yes/No)</t>
+          <t>CT display names that do not match Domain_Name directly (7 rows)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Instrument_Domain_Rules</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
+          <t>Keyword-to-domain mapping for non-extensible instrument codelists (3 rows)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Non_Observation_Datasets</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Brief notes on domain status or version history</t>
+          <t>SDTMIG v3.4 datasets that are not domains of observations, each with the reason (5 rows)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>IG_Name</t>
+          <t>Consumer_Exclusions</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Domain name in the SDTMIG v3.4 table of contents (the sheet name for MB, MS, PC, PP); empty for domains added from CT</t>
+          <t>Domains a Findings consumer leaves out of its scope, each reason stated as testable claims (4 rows)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>IG_Class</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Class in the SDTMIG v3.4 variable table; empty for domains added from CT</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Variable_Meaning</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (26 rows)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="n"/>
       <c r="B35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>CODELIST_OVERRIDES COLUMNS</t>
-        </is>
-      </c>
+          <t>COLUMN DESCRIPTIONS</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CT_Display_Name</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
+          <t>Two-letter SDTM domain abbreviation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Domain_Name</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
+          <t>Domain name used to match SDTM CT codelist names (sdtm-test-codes/notebooks/SDTM_CT_Extract.ipynb); the SDTMIG v3.4 name for most domains, the C66734 name for domains added from CT. IG_Name has the IG name.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Override_Type</t>
+          <t>Observation_Class</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+          <t>SDTM observation class: Findings, Events, Interventions, Special-Purpose, Trial Design. FA and SR are Findings here (the consumers filter on it); IG_Class has Findings About.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>SDTMIG_Section</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Description of the mismatch</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
+          <t>Section number in the SDTMIG v3.4 table of contents (empty for domains added from CT). MB, MS (6.3.5.7) and PC, PP (6.3.5.9) are listed only under a group heading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Has_Test_Codes</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain uses --TESTCD/--TEST variables (Yes/No)</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Specimen_Based</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Whether the domain is specimen-based: listed under SDTMIG v3.4 Section 6.3.5 Specimen-based Findings Domains (Yes/No)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Keyword</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
+          <t>Whether the domain is a subject-level measurement domain (Yes/No). Measurement_Findings takes its scope from this flag, minus exclusions named in the notebook.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation</t>
+          <t>Brief notes on domain status or version history</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>IG_Name</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Description and examples of instrument types in this category</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+          <t>Domain name in the SDTMIG v3.4 table of contents (the sheet name for MB, MS, PC, PP); empty for domains added from CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>IG_Class</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Class in the SDTMIG v3.4 variable table; empty for domains added from CT</t>
+        </is>
+      </c>
+    </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>NON_OBSERVATION_DATASETS COLUMNS</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 dataset name</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>CODELIST_OVERRIDES COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IG_Name</t>
+          <t>CT_Display_Name</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Name in the SDTMIG v3.4 table of contents (8.4.1 Supplemental Qualifiers (SUPP--) for SUPPQUAL)</t>
+          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>IG_Class</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Class in the SDTMIG v3.4 variable table</t>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG_Section</t>
+          <t>Override_Type</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Section number in the SDTMIG v3.4 table of contents</t>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Reason</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Why the dataset is not listed in Domains</t>
+          <t>Description of the mismatch</t>
         </is>
       </c>
     </row>
@@ -995,19 +979,19 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>CONSUMER_EXCLUSIONS COLUMNS</t>
+          <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
+          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
@@ -1019,198 +1003,270 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Domain excluded from that consumer's scope</t>
+          <t>Target SDTM domain abbreviation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Claim_ID</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Identifier of one testable claim behind the exclusion</t>
+          <t>Description and examples of instrument types in this category</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Claim</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>NON_OBSERVATION_DATASETS COLUMNS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 dataset name</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>IG_Name</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Name in the SDTMIG v3.4 table of contents (8.4.1 Supplemental Qualifiers (SUPP--) for SUPPQUAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>IG_Class</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Class in the SDTMIG v3.4 variable table</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SDTMIG_Section</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Section number in the SDTMIG v3.4 table of contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>The exclusion reason as recorded in the consumer notebook</t>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>VARIABLE_MEANING COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Key_Source</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name), Interpretation_Context (Domain + variable, with COSMoS content); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Why the dataset is not listed in Domains</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>CONSUMER_EXCLUSIONS COLUMNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Key</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>The variable, or the axis for Key_Compare rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Basis_Note</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>What each source states, by sheet and column; the rule, where one is used</t>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Domain excluded from that consumer's scope</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>proposed / accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Claim_ID</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Identifier of one testable claim behind the exclusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>KNOWN LIMITATIONS</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Variable-level metadata (key variables, permissible variables) is not included.</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="n"/>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>The exclusion reason as recorded in the consumer notebook</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>CDISC publishes it as the SDTM v2.0 and SDTMIG v3.4 variable tables (sign-in at cdisc.org). Local copies sit in sdtm-domain-reference/downloads/ (gitignored); domain-behaviour reads them.</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="n"/>
       <c r="B73" s="2" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SDTM v3.0 is under review and may add or change domains.</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="n"/>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>VARIABLE_MEANING COLUMNS</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>MO (Morphology) was decommissioned in v3.4 and is not listed.</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="n"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Key_Source</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name), Interpretation_Context (Domain + variable, with COSMoS content); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG_Section, IG_Name, IG_Class, Has_Test_Codes and Specimen_Based, and the Non_Observation_Datasets sheet, are checked against SDTMIG v3.4 by sdtm-findings-graph/notebooks/Scope_Check.ipynb (section 5).</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="n"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>The variable, or the axis for Key_Compare rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Basis_Note</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>What each source states, by sheet and column; the rule, where one is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>proposed / accepted</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -2011,7 +2011,7 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>From SDTMIG-PGx v1.0</t>
+          <t>From SDTMIG-PGx v1.0. Events: specimen handling (collection, culturing, preparation, transport, storage in its COSMoS DSSs). Parent and derived specimens are related in RELSPEC (sheet Non_Observation_Datasets).</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
@@ -2893,7 +2893,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>SDTMIG v3.4 binds no codelist to PCTESTCD (the analyte is sponsor-defined), so SDTM_Test_Identity has no PC rows.</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>Pharmacokinetics Concentrations</t>
@@ -2943,7 +2947,7 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>Paired with PC</t>
+          <t>Paired with PC. PPTESTCD is bound to PKPARMCD (C85839), which SDTM_CT_Extract does not read by decision (its section 5b), so SDTM_Test_Identity has no PP rows.</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -3643,7 +3643,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>TAUG-CV</t>
+          <t>TAUG-CV (CDISC Therapeutic Area User Guide for Cardiovascular Studies)</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (26 rows)</t>
+          <t>Our position on what a variable or axis means for the observable, Findings only, each with a stated basis (27 rows)</t>
         </is>
       </c>
     </row>
@@ -880,389 +880,401 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Immunogenicity</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Brief notes on domain status or version history</t>
+          <t>Whether the domain is covered by Immunogenicity_Findings (Yes/No). Checked before Specimen_Based: IS is Specimen_Based = Yes (SDTMIG v3.4 Section 6.3.5) and Immunogenicity = Yes, so it goes to Immunogenicity_Findings; its exclusion from Specimen_Findings (Consumer_Exclusions IS-1, IS-2) stays and is tested on every release.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>IG_Name</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Domain name in the SDTMIG v3.4 table of contents (the sheet name for MB, MS, PC, PP); empty for domains added from CT</t>
+          <t>Brief notes on domain status or version history</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>IG_Name</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Domain name in the SDTMIG v3.4 table of contents (the sheet name for MB, MS, PC, PP); empty for domains added from CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
           <t>IG_Class</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Class in the SDTMIG v3.4 variable table; empty for domains added from CT</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n"/>
-      <c r="B47" s="2" t="n"/>
-    </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>CODELIST_OVERRIDES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CT_Display_Name</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>CT_Display_Name</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
+          <t>The codelist display name from NCI EVS (after stripping " Test Code")</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Override_Type</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+          <t>Target SDTM domain abbreviation (empty for Cross-domain)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>Override_Type</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Naming (label mismatch), Subset (body-system sub-codelist), or Cross-domain (test code codelist shared by several domains; Domain empty)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Description of the mismatch</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-    </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>INSTRUMENT_DOMAIN_RULES COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>Keyword</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Keyword</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Target SDTM domain abbreviation</t>
+          <t>Instrument class. Matched first as the prefix "CDISC &lt;Keyword&gt; " of the codelist NCI Preferred Term, then as a substring of the codelist display name</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Target SDTM domain abbreviation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>Description and examples of instrument types in this category</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n"/>
-      <c r="B58" s="2" t="n"/>
-    </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>NON_OBSERVATION_DATASETS COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>SDTMIG v3.4 dataset name</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>IG_Name</t>
+          <t>Dataset</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Name in the SDTMIG v3.4 table of contents (8.4.1 Supplemental Qualifiers (SUPP--) for SUPPQUAL)</t>
+          <t>SDTMIG v3.4 dataset name</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>IG_Class</t>
+          <t>IG_Name</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Class in the SDTMIG v3.4 variable table</t>
+          <t>Name in the SDTMIG v3.4 table of contents (8.4.1 Supplemental Qualifiers (SUPP--) for SUPPQUAL)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SDTMIG_Section</t>
+          <t>IG_Class</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Section number in the SDTMIG v3.4 table of contents</t>
+          <t>Class in the SDTMIG v3.4 variable table</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>SDTMIG_Section</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Section number in the SDTMIG v3.4 table of contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Why the dataset is not listed in Domains</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n"/>
-      <c r="B65" s="2" t="n"/>
-    </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>CONSUMER_EXCLUSIONS COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Domain excluded from that consumer's scope</t>
+          <t>Findings consumer notebook that reads the row (Specimen_Findings, Measurement_Findings, Instrument_Findings)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Claim_ID</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Identifier of one testable claim behind the exclusion</t>
+          <t>Domain excluded from that consumer's scope</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Claim_ID</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
+          <t>Identifier of one testable claim behind the exclusion</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+          <t>What the published COSMoS content must show for the exclusion reason to hold</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Machine form of the claim, evaluated by domain-behaviour/notebooks/Domain_Behaviour.ipynb: no_fanout, no_axis, not_axis:&lt;axis&gt;, axis_all:&lt;axis&gt;, not_primary:&lt;axis&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>The exclusion reason as recorded in the consumer notebook</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n"/>
-      <c r="B73" s="2" t="n"/>
-    </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>VARIABLE_MEANING COLUMNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Key_Source</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name), Interpretation_Context (Domain + variable, with COSMoS content); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Domain</t>
+          <t>Key_Source</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
+          <t>Sheet of domain-behaviour/interim/Domain_Behaviour.xlsx the key must exist in: Variable_Evidence (Domain + variable), Key_Compare (axis; Domain empty), Rater_COSMoS_EVAL (variable_name), Interpretation_Context (Domain + variable, with COSMoS content); or LOINC_Subject_State: sheet Subject_State of cosmos-bc-dss/reports/COSMoS_Observable_LOINC_Check.xlsx (state_variable)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The variable, or the axis for Key_Compare rows</t>
+          <t>SDTM domain, Findings class; empty for Key_Compare rows</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
+          <t>The variable, or the axis for Key_Compare rows</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
+          <t>The part of the observable key it identifies: component, system, method, scale; not part of the observable (the published reason in Basis_Note); or open</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Basis_Note</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What each source states, by sheet and column; the rule, where one is used</t>
+          <t>sources agree / sources disagree, decided by a stated rule / standards silent, open</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Basis_Note</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>What each source states, by sheet and column; the rule, where one is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>proposed / accepted</t>
         </is>
@@ -1279,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1289,8 +1301,10 @@
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1331,15 +1345,20 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>Immunogenicity</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>IG_Name</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>IG_Class</t>
         </is>
@@ -1381,13 +1400,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Special-Purpose</t>
         </is>
@@ -1429,13 +1453,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Demographics</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Special-Purpose</t>
         </is>
@@ -1477,13 +1506,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Subject Elements</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Special-Purpose</t>
         </is>
@@ -1525,13 +1559,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Subject Disease Milestones</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Special-Purpose</t>
         </is>
@@ -1573,13 +1612,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Subject Visits</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Special-Purpose</t>
         </is>
@@ -1621,13 +1665,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Procedure Agents</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1669,13 +1718,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Concomitant/Prior Medications</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1717,13 +1771,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Exposure as Collected</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1765,13 +1824,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1813,17 +1877,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>New in v3.4 scope</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Meal Data</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1865,13 +1934,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Procedures</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1913,13 +1987,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Substance Use</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Interventions</t>
         </is>
@@ -1961,13 +2040,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Adverse Events</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2009,17 +2093,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>From SDTMIG-PGx v1.0. Events: specimen handling (collection, culturing, preparation, transport, storage in its COSMoS DSSs). Parent and derived specimens are related in RELSPEC (sheet Non_Observation_Datasets).</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Biospecimen Events</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2061,13 +2150,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Clinical Events</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2109,13 +2203,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Disposition</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2157,13 +2256,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Protocol Deviations</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2205,13 +2309,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Healthcare Encounters</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2253,13 +2362,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Medical History</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Events</t>
         </is>
@@ -2301,13 +2415,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Product Accountability</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2349,13 +2468,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Death Details</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2397,13 +2521,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>ECG Test Results</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2445,13 +2574,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Inclusion/Exclusion Criteria Not Met</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2493,17 +2627,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>From SDTMIG-PGx v1.0</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Biospecimen Findings</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2545,17 +2684,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>New in v3.4</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Cell Phenotype Findings</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2597,17 +2741,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>New in v3.4</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Genomics Findings</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2649,17 +2798,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>Scope expanded in v3.4</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Immunogenicity Specimen Assessments</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2701,13 +2855,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Laboratory Test Results</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2749,13 +2908,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Microbiology Specimen</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2797,13 +2961,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Microscopic Findings</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2845,13 +3014,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Microbiology Susceptibility</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2893,17 +3067,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>SDTMIG v3.4 binds no codelist to PCTESTCD (the analyte is sponsor-defined), so SDTM_Test_Identity has no PC rows.</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Pharmacokinetics Concentrations</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2945,17 +3124,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>Paired with PC. PPTESTCD is bound to PKPARMCD (C85839), which SDTM_CT_Extract does not read by decision (its section 5b), so SDTM_Test_Identity has no PP rows.</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Pharmacokinetics Parameters</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -2997,13 +3181,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Findings About Events or Interventions</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Findings About</t>
         </is>
@@ -3045,17 +3234,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Functional Tests</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3097,13 +3291,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Musculoskeletal System Findings</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3145,17 +3344,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Questionnaires</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3197,13 +3401,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Reproductive System Findings</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3245,17 +3454,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>QRS instrument domain</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Disease Response and Clin Classification</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3297,13 +3511,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Subject Characteristics</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3345,13 +3564,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Skin Response</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="K42" s="5" t="inlineStr">
         <is>
           <t>Findings About</t>
         </is>
@@ -3393,13 +3617,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Subject Status</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="K43" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3441,17 +3670,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>Oncology</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Tumor/Lesion Results</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="K44" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3493,17 +3727,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>Oncology</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Tumor/Lesion Identification</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="K45" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3545,13 +3784,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Urinary System Findings</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="K46" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3593,13 +3837,18 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Vital Signs</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="K47" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3641,17 +3890,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>TAUG-CV (CDISC Therapeutic Area User Guide for Cardiovascular Studies)</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Cardiovascular System Findings</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="K48" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -3693,13 +3947,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Trial Arms</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="K49" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3741,13 +4000,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Trial Disease Assessments</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="K50" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3789,13 +4053,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Trial Elements</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="K51" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3837,13 +4106,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Trial Inclusion/Exclusion Criteria</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="K52" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3885,13 +4159,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Trial Summary</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3933,13 +4212,18 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Trial Visits</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="K54" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -3981,17 +4265,22 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>Body System Findings domain (introduced SDTMIG v3.3, 2018). COSMoS BC/DSS coverage added in 2026-03 package: 135 DSS, primarily pulmonary function and respiratory mechanics.</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Respiratory System Findings</t>
         </is>
       </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -4029,7 +4318,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
@@ -4067,7 +4361,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
@@ -4105,7 +4404,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
@@ -4143,7 +4447,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
@@ -4181,7 +4490,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Consumer class pending published COSMoS content.</t>
         </is>
@@ -4223,17 +4537,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>In SDTMIG v3.4 (6.3.7.4). Listed here first on 2026-10-01 from SDTM CT C66734 as a domain not in the IG; corrected 2026-10-12. Consumer class pending published COSMoS content.</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr">
+      <c r="J61" s="5" t="inlineStr">
         <is>
           <t>Nervous System Findings</t>
         </is>
       </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="K61" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -4275,17 +4594,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>In SDTMIG v3.4 (6.3.7.5). Listed here first on 2026-10-01 from SDTM CT C66734 as a domain not in the IG; corrected 2026-10-12. Consumer class pending published COSMoS content.</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr">
+      <c r="J62" s="5" t="inlineStr">
         <is>
           <t>Ophthalmic Examinations</t>
         </is>
       </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="K62" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -4323,7 +4647,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device characteristics, not an observation of the subject: no consumer class.</t>
         </is>
@@ -4361,7 +4690,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Device settings in use, not an observation of the subject: no consumer class.</t>
         </is>
@@ -4399,7 +4733,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>Not in SDTMIG v3.4. Added 2026-10-01 from SDTM CT C66734 (2026-09-25), which defines it as a findings domain. Tobacco product sample testing, not an observation of the subject: no consumer class.</t>
         </is>
@@ -4441,17 +4780,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>Added 2026-10-12 from SDTMIG v3.4.</t>
         </is>
       </c>
-      <c r="I66" s="5" t="inlineStr">
+      <c r="J66" s="5" t="inlineStr">
         <is>
           <t>Physical Examination</t>
         </is>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="K66" s="5" t="inlineStr">
         <is>
           <t>Findings</t>
         </is>
@@ -4493,17 +4837,22 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>Added 2026-10-12 from SDTMIG v3.4.</t>
         </is>
       </c>
-      <c r="I67" s="5" t="inlineStr">
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>Trial Disease Milestones</t>
         </is>
       </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="K67" s="5" t="inlineStr">
         <is>
           <t>Trial Design</t>
         </is>
@@ -5167,7 +5516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5614,7 +5963,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5631,49 +5980,54 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LBTESTCD</t>
+          <t>ISTSTOPO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>sources disagree, decided by a stated rule</t>
+          <t>standards silent, open</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COSMoS puts GLUC and GLUCPE under one BC (C105585). SDTM CT publishes them as separate LBTESTCD terms with their own NCIt codes and definitions (GLUC C105585; GLUCPE C163446, "plasma equivalent glucose"). The key separates them; the fan-out does not. Rule (adopted 2026-10-08): a separate SDTM CT test term with its own NCIt code is a separate component (identity keyed on NCIt codes, Observables_Direction step 2). SDTM v2.0 and SDTMIG v3.4: Topic.</t>
+          <t>COSMoS: value list only (TSTOPOBJ), never assigned; on 64 DSSs in 2 BCs (C187786, C198280). There the DSSs come in 32 pairs with the same binding agent: SCREEN;CONFIRM with result POSITIVE;NEGATIVE and no units (DS code ending PN), QUANTIFY with units. So in COSMoS the tier goes with the scale, which the scale row already separates. SDTMIG v3.4: Variable Qualifier; IS Assumption 8, nonextensible codelist SCREEN, CONFIRM, QUANTIFY; IS Example 1 uses it for the tiers of ADA testing, 'to provide uniqueness to each row of record'. Two readings: the tier is part of the observable, or it is the operational step that produces an observable already told apart by scale. No source says which.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>proposed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Key_Compare</t>
+          <t>Variable_Evidence</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>LBTESTCD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>scale</t>
+          <t>component</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5683,7 +6037,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rule (decided 2026-10-06): result scale is treated as distinguishing an observable, on the standards' own grounds: DSSs of one BC differ by scale, and LOINC has scale as an axis. No claim that it is clinically right. Disagreement: the fan-out reads units present or absent; the key reads the --ORRES data type (Key_Compare). COSMoS publishes result scale per BC, not per DSS (Scale_Units). The rule does not settle which per-DSS reading is right.</t>
+          <t>COSMoS puts GLUC and GLUCPE under one BC (C105585). SDTM CT publishes them as separate LBTESTCD terms with their own NCIt codes and definitions (GLUC C105585; GLUCPE C163446, "plasma equivalent glucose"). The key separates them; the fan-out does not. Rule (adopted 2026-10-08): a separate SDTM CT test term with its own NCIt code is a separate component (identity keyed on NCIt codes, Observables_Direction step 2). SDTM v2.0 and SDTMIG v3.4: Topic.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5695,32 +6049,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Variable_Evidence</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GF</t>
+          <t>Key_Compare</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GFANMETH</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>standards silent, open</t>
+          <t>sources disagree, decided by a stated rule</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions) confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing).</t>
+          <t>Rule (decided 2026-10-06): result scale is treated as distinguishing an observable, on the standards' own grounds: DSSs of one BC differ by scale, and LOINC has scale as an axis. No claim that it is clinically right. Disagreement: the fan-out reads units present or absent; the key reads the --ORRES data type (Key_Compare). COSMoS publishes result scale per BC, not per DSS (Scale_Units). The rule does not settle which per-DSS reading is right.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5737,12 +6086,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LBCAT</t>
+          <t>GFANMETH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5757,7 +6106,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions) confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing).</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5774,12 +6123,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RSCAT</t>
+          <t>LBCAT</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5794,7 +6143,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5811,12 +6160,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GF</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GFSYMTYP</t>
+          <t>RSCAT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5831,7 +6180,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_POSITION_FOR, "is the type of genomic entity that is the position of the result in", codelist SYMTYPGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --SYM (the gene symbol).</t>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5853,22 +6202,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GFINHERT</t>
+          <t>GFSYMTYP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>not part of the observable</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>sources agree</t>
+          <t>standards silent, open</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>COSMoS: IS_ATTRIBUTE_FOR, "indicates heritability of the genetic variant in", codelist INHERTGF. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --ORRES, --STRESC, --STRESN. Both say it qualifies the result, not the test.</t>
+          <t>COSMoS: predicate IS_POSITION_FOR, "is the type of genomic entity that is the position of the result in", codelist SYMTYPGF. Separates DSSs; outside our seven axes and not in the key. No source says whether it changes the observation. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --SYM (the gene symbol).</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5885,12 +6234,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>GF</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TRGRPID</t>
+          <t>GFINHERT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5905,7 +6254,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts. SDTMIG v3.4 TR Assumptions 1 and 2 (IG_Assumptions): --GRPID 'may be used for other purposes, per the SDTM', so TR/TU links use --LNKID/--LNKGRP instead.</t>
+          <t>COSMoS: IS_ATTRIBUTE_FOR, "indicates heritability of the genetic variant in", codelist INHERTGF. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --ORRES, --STRESC, --STRESN. Both say it qualifies the result, not the test.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -5922,27 +6271,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VSPOS</t>
+          <t>TRGRPID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>not part of the observable</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>standards silent, open</t>
+          <t>sources agree</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. The SDTMIG v3.4 VS Assumptions do not discuss VSPOS; LB Assumption 8 (IG_Assumptions) names LBPOS (in LB) among the LOINC-associated aspects of a test.</t>
+          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts. SDTMIG v3.4 TR Assumptions 1 and 2 (IG_Assumptions): --GRPID 'may be used for other purposes, per the SDTM', so TR/TU links use --LNKID/--LNKGRP instead.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -5954,17 +6303,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rater_COSMoS_EVAL</t>
+          <t>Variable_Evidence</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QSEVAL</t>
+          <t>VSPOS</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5979,7 +6328,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property.</t>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. The SDTMIG v3.4 VS Assumptions do not discuss VSPOS; LB Assumption 8 (IG_Assumptions) names LBPOS (in LB) among the LOINC-associated aspects of a test.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -5996,12 +6345,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>RSEVAL</t>
+          <t>QSEVAL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -6016,7 +6365,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7 (IG_Assumptions): RSEVALID with RSEVAL gives detail of who provides the assessment.</t>
+          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6028,17 +6377,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LOINC_Subject_State</t>
+          <t>Rater_COSMoS_EVAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LBFAST</t>
+          <t>RSEVAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6053,7 +6402,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2).</t>
+          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7 (IG_Assumptions): RSEVALID with RSEVAL gives detail of who provides the assessment.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6065,17 +6414,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Interpretation_Context</t>
+          <t>LOINC_Subject_State</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>QS</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>QSEVINTX</t>
+          <t>LBFAST</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6090,12 +6439,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Interpretation_Context: COSMoS_Use = always assigned in QS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2).</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>accepted</t>
         </is>
       </c>
     </row>
@@ -6107,12 +6456,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>QS</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RSEVINTX</t>
+          <t>QSEVINTX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6127,7 +6476,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+          <t>Interpretation_Context: COSMoS_Use = always assigned in QS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6149,25 +6498,62 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>RSEVINTX</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>standards silent, open</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Interpretation_Context</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>RSEVLINT</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>standards silent, open</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -5842,22 +5842,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>component</t>
+          <t>open</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sources agree</t>
+          <t>standards silent, open</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. Held 2026-10-08 for the DEC label; resolved: SDTM v2.0 and SDTMIG v3.4 both give Variable Qualifier of --TESTCD.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", codelist ISFTSDTL; DEC label not stated on all DSSs. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD; SDTMIG v3.4 CDISC Notes: 'Further description of ISTESTCD and ISTEST', no codelist in the IG table. SDTM CT ISFTSDTL (extensible) holds neutralisation and inhibition levels (e.g. 50% NEUTRALIZATION TITER, 50% INHIBITORY CONCENTRATION) beside score systems whose NCIt definitions describe a classification of the amount of allergen-specific antibody (RAST SCORE, MAST 5-CLASS, MAST 7-CLASS). COSMoS assigns only RAST SCORE and MAST 7-CLASS: every such DSS has an ordinal class value list and no units, and every DSS with the same BC and binding agent and no ISTSTDTL has units, so the scale row already separates them. The IS table has no result-scale variable (LB has LBRESSCL). Two readings: the test detail is part of the observable, or, for score systems, it is the form of the result of an observable already told apart by scale. No source says which. Changed 2026-10-31 from component / sources agree.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>accepted</t>
+          <t>proposed</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT. Quoted in SDTMIG_Statements.xlsx: ISBDAGNT-Notes, IS-A7, IS-A7a, IS-A7b.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'.</t>
+          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions): 'GFMETHOD lists wet lab techniques …; methods related to specimen processing or reagents are not represented in GFMETHOD.'</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 GF Assumption 8: 'GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.' Quoted in SDTMIG_Statements.xlsx: GF-A8.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 MB Assumption 1 (IG_Assumptions): 'DETECTION' for tests that identify an organism; for a characteristic, 'the name of the characteristic being described (e.g., COLONY COUNT, VIRAL LOAD)'.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 MB Assumption 1a, 1c: 'DETECTION' for tests that identify an organism; for a characteristic, 'the name of the characteristic being described (e.g., COLONY COUNT, VIRAL LOAD)'. Quoted in SDTMIG_Statements.xlsx: MB-A1a, MB-A1c, MBTSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7 (IG_Assumptions): two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT. Quoted in SDTMIG_Statements.xlsx: ISBDAGNT-Notes, IS-A7, IS-A7a, IS-A7b.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7: two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT. Quoted in SDTMIG_Statements.xlsx: ISBDAGNT-Notes, IS-A7, IS-A7a, IS-A7b.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>COSMoS: value list only (TSTOPOBJ), never assigned; on 64 DSSs in 2 BCs (C187786, C198280). There the DSSs come in 32 pairs with the same binding agent: SCREEN;CONFIRM with result POSITIVE;NEGATIVE and no units (DS code ending PN), QUANTIFY with units. So in COSMoS the tier goes with the scale, which the scale row already separates. SDTMIG v3.4: Variable Qualifier; IS Assumption 8, nonextensible codelist SCREEN, CONFIRM, QUANTIFY; IS Example 1 uses it for the tiers of ADA testing, 'to provide uniqueness to each row of record'. Two readings: the tier is part of the observable, or it is the operational step that produces an observable already told apart by scale. No source says which.</t>
+          <t>COSMoS: value list only (TSTOPOBJ), never assigned; on 64 DSSs in 2 BCs (C187786, C198280). There the DSSs come in 32 pairs with the same binding agent: SCREEN;CONFIRM with result POSITIVE;NEGATIVE and no units (DS code ending PN), QUANTIFY with units. So in COSMoS the tier goes with the scale, which the scale row already separates. SDTMIG v3.4: Variable Qualifier; IS Assumption 8, nonextensible codelist SCREEN, CONFIRM, QUANTIFY; IS Example 1 uses it for the tiers of ADA testing, 'to provide uniqueness to each row of record'. Two readings: the tier is part of the observable, or it is the operational step that produces an observable already told apart by scale. No source says which. Quoted in SDTMIG_Statements.xlsx: IS-A8.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 (IG_Assumptions) confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing).</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing). Quoted in SDTMIG_Statements.xlsx: GF-A8.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown. Disease response 1 quoted in SDTMIG_Statements.xlsx: RS-DR-A1.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. The SDTMIG v3.4 VS Assumptions do not discuss VSPOS; LB Assumption 8 (IG_Assumptions) names LBPOS (in LB) among the LOINC-associated aspects of a test.</t>
+          <t>COSMoS: predicate IS_SUBJECT_STATE_FOR, "is the subject position during performance of the test in", codelist POSITION. Value list only. COSMoS calls it subject state; no source says whether subject state is part of the observable. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): position-free and position-qualified codes side by side (^sitting, ^standing, ^supine); COSMoS assigns VSPOS on no DSS. LOINC offers position as a refinement, not as a requirement. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. The SDTMIG v3.4 VS Assumptions do not discuss VSPOS; LB Assumption 8 names LBPOS among the LOINC-associated aspects of a test; LBPOS is not in the SDTMIG v3.4 LB variable table (it is the SDTM v2.0 Findings variable --POS). Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8 (IG_Assumptions): LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2).</t>
+          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8: LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2). Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -5815,7 +5815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 CDISC Notes: 'Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.' COSMoS assigns GFTSTDTL on every GF DSS; it differs between the DSSs of every GF BC with more than one DSS, and in most of them it is the only assigned value that differs. Siblings report different things (e.g. READ DEPTH, GENOTYPE, PREDICTED AMINO ACID CHANGE under one BC), often with the same data type. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own role. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own role. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes. SDTMIG v3.4 CDISC Notes: 'Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.' In COSMoS MITSTDTL is the only assigned value that separates the DSSs of one BC (Allred proportion positive score, staining intensity score and total score, for the estrogen and for the progesterone receptor); all are integer without units, so scale does not separate them. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -5815,7 +5815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 CDISC Notes: 'Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.' COSMoS assigns GFTSTDTL on every GF DSS; it differs between the DSSs of every GF BC with more than one DSS, and in most of them it is the only assigned value that differs. Siblings report different things (e.g. READ DEPTH, GENOTYPE, PREDICTED AMINO ACID CHANGE under one BC), often with the same data type. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 CDISC Notes: 'Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.' COSMoS assigns GFTSTDTL on every GF DSS; it differs between the DSSs of every GF BC with more than one DSS, and in most of them it is the only assigned value that differs. Siblings report different things (e.g. READ DEPTH, GENOTYPE, PREDICTED AMINO ACID CHANGE under one BC), often with the same data type. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: GFTSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2 (IG_Assumptions): 'MITSTDTL further qualifies the record' — the IG prose matches its own role. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes. SDTMIG v3.4 CDISC Notes: 'Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.' In COSMoS MITSTDTL is the only assigned value that separates the DSSs of one BC (Allred proportion positive score, staining intensity score and total score, for the estrogen and for the progesterone receptor); all are integer without units, so scale does not separate them. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2: 'MITSTDTL further qualifies the record' — the IG prose matches its own role; its examples are 'H SCORE TOTAL SCORE', 'STAINING INTENSITY', 'PERCENT POSITIVE CELL'. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes. SDTMIG v3.4 CDISC Notes: 'Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.' In COSMoS MITSTDTL is the only assigned value that separates the DSSs of one BC (Allred proportion positive score, staining intensity score and total score, for the estrogen and for the progesterone receptor); all are integer without units, so scale does not separate them. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: MI-A2, MITSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing). Quoted in SDTMIG_Statements.xlsx: GF-A8.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing). Quoted in SDTMIG_Statements.xlsx: GF-A8, GFANMETH-Notes.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (IG_Assumptions; disease response 1, 6, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown. Disease response 1 quoted in SDTMIG_Statements.xlsx: RS-DR-A1.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in", the same as LBCAT. SDTM CT codelist ONCRSCAT, Category of Oncology Response Assessment: the response criteria. Not in the key. No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier; the IG notes that the RSCAT codelist depends on whether the records are oncology response criteria or another clinical classification. SDTMIG v3.4 RS Assumptions (disease response 1, 6b, 9; clinical classifications 2): RSCAT 'is used to group a set of assessments based on' a disease response criterion or a clinical classification; 'UNSPECIFIED' when the criteria are unknown. Quoted in SDTMIG_Statements.xlsx: RS-DR-A1, RS-DR-A6b, RS-DR-A9, RS-CC-A2.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts. SDTMIG v3.4 TR Assumptions 1 and 2 (IG_Assumptions): --GRPID 'may be used for other purposes, per the SDTM', so TR/TU links use --LNKID/--LNKGRP instead.</t>
+          <t>SDTM v2.0 and SDTMIG v3.4: Identifier, "used to link together a block of related records within a subject in a domain". COSMoS states nothing (no predicate, no codelist). One source states it, none contradicts. SDTMIG v3.4 TR Assumptions 1 and 2: --GRPID 'may be used for other purposes, per the SDTM', so TR/TU links use --LNKID/--LNKGRP instead. Quoted in SDTMIG_Statements.xlsx: TR-A1, TR-A2.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property.</t>
+          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property. SDTMIG v3.4 QS Assumption 8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'; supplemental qualifiers may be used if needed. COSMoS assigns QSEVAL = CAREGIVER on the DSSs of TTS ACCEPTABILITY SURVEY - LZZT. Quoted in SDTMIG_Statements.xlsx: QS-A8.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7 (IG_Assumptions): RSEVALID with RSEVAL gives detail of who provides the assessment.</t>
+          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7: RSEVALID with RSEVAL gives detail of who provides the assessment. COSMoS assigns RSEVAL = INVESTIGATOR on Child-Pugh Classification DSSs (RSCAT codelist CCCAT, a clinical classification); the value list INVESTIGATOR;INDEPENDENT ASSESSOR is on oncology response DSSs (ONCRSCAT), and INVESTIGATOR;DERMATOLOGIST on PASI (CCCAT). The RS Clinical Classifications Use Case Assumptions (p338) carry the QRS assumption also quoted as QS-A8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'. Quoted in SDTMIG_Statements.xlsx: RS-DR-A7, QS-A8 (the RS copy cannot be selected; see its ReadMe).</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">

--- a/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
+++ b/sdtm-domain-reference/machine_actionable/SDTM_Domain_Metadata.xlsx
@@ -5593,7 +5593,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). LOINC system agrees (LOINC_Compare); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
+          <t>COSMoS: predicate IS_SPECIMEN_TESTED_IN, "is the specimen tested in", codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare in Domain_Behaviour). LOINC system agrees (LOINC_Compare in Domain_Behaviour); the exceptions are COSMoS pin errors reported by COSMoS_Observable_LOINC_Check. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist GENSMP. Fan-out axis specimen and key part system agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist GENSMP. One source states it, none contradicts. Fan-out axis specimen and key part system agree (Key_Compare in Domain_Behaviour). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist SPECTYPE. Fan-out axis specimen and key part system agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS only: predicate IS_SPECIMEN_TESTED_IN, codelist SPECTYPE. One source states it, none contradicts. Fan-out axis specimen and key part system agree (Key_Compare in Domain_Behaviour). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare). LOINC method agrees where COSMoS separates by method (LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method for the test in", DEC Test Method, codelist METHOD. Fan-out axis method and key part method agree (Key_Compare in Domain_Behaviour). LOINC method agrees where COSMoS separates by method (LOINC_Compare in Domain_Behaviour). SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 LB Assumption 8: with LBTEST and LBORRESU, 'the aspects of a test that are associated with a LOINC code'. Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 GF Assumption 8: 'GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.' Quoted in SDTMIG_Statements.xlsx: GF-A8.</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. One source states it, none contradicts. Fan-out and key agree (Key_Compare in Domain_Behaviour). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them. SDTMIG v3.4 GF Assumption 8: 'GFMETHOD lists wet lab techniques for the execution of genomics or genetic testing. Methods related to specimen processing or reagents are not represented in GFMETHOD.' Quoted in SDTMIG_Statements.xlsx: GF-A8.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. Fan-out and key agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
+          <t>COSMoS only: predicate SPECIFIES, DEC Test Method, codelist METHOD. One source states it, none contradicts. Fan-out and key agree (Key_Compare in Domain_Behaviour). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, the same role as --POS and --FAST; the role does not separate them.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 CDISC Notes: 'Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.' COSMoS assigns GFTSTDTL on every GF DSS; it differs between the DSSs of every GF BC with more than one DSS, and in most of them it is the only assigned value that differs. Siblings report different things (e.g. READ DEPTH, GENOTYPE, PREDICTED AMINO ACID CHANGE under one BC), often with the same data type. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: GFTSTDTL-Notes.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist GFTSDTL. Fan-out axis test detail and key part component agree (Key_Compare in Domain_Behaviour). GF DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 CDISC Notes: 'Description of a reportable qualifying the assessment in GFTESTCD and GFTEST.' COSMoS assigns GFTSTDTL on every GF DSS; it differs between the DSSs of every GF BC with more than one DSS, and in most of them it is the only assigned value that differs. Siblings report different things (e.g. READ DEPTH, GENOTYPE, PREDICTED AMINO ACID CHANGE under one BC), often with the same data type. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: GFTSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare). LOINC not read for MB (not in LOINC_Compare). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 MB Assumption 1a, 1c: 'DETECTION' for tests that identify an organism; for a characteristic, 'the name of the characteristic being described (e.g., COLONY COUNT, VIRAL LOAD)'. Quoted in SDTMIG_Statements.xlsx: MB-A1a, MB-A1c, MBTSTDTL-Notes.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate SPECIFIES, "further describes the test in", DEC Measurement, Test or Examination Detail, codelist MBFTSDTL. Fan-out and key agree (Key_Compare in Domain_Behaviour). LOINC not read for MB (not in LOINC_Compare in Domain_Behaviour). SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 MB Assumption 1a, 1c: 'DETECTION' for tests that identify an organism; for a characteristic, 'the name of the characteristic being described (e.g., COLONY COUNT, VIRAL LOAD)'. Quoted in SDTMIG_Statements.xlsx: MB-A1a, MB-A1c, MBTSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2: 'MITSTDTL further qualifies the record' — the IG prose matches its own role; its examples are 'H SCORE TOTAL SCORE', 'STAINING INTENSITY', 'PERCENT POSITIVE CELL'. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes. SDTMIG v3.4 CDISC Notes: 'Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.' In COSMoS MITSTDTL is the only assigned value that separates the DSSs of one BC (Allred proportion positive score, staining intensity score and total score, for the estrogen and for the progesterone receptor); all are integer without units, so scale does not separate them. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: MI-A2, MITSTDTL-Notes.</t>
+          <t>COSMoS: SPECIFIES, "further describes the test in", codelist MIFTSDTL. SDTM v2.0: Variable Qualifier of --TESTCD, like the other --TSTDTL rows. SDTMIG v3.4 MI: Record Qualifier; MI Assumption 2: 'MITSTDTL further qualifies the record' — the IG prose matches its own role; its examples are 'H SCORE TOTAL SCORE', 'STAINING INTENSITY', 'PERCENT POSITIVE CELL'. The sources differ on role, not on the observable: the SDTM roles do not separate identifying qualifiers from subject state (--SPEC and --METHOD are Record Qualifiers too; Variable_Evidence in Domain_Behaviour). Rule (2026-10-08): the role does not decide; a separate SDTM CT term with its own NCIt code is a separate component (the LBTESTCD rule). The assigned MITSTDTL values are MIFTSDTL terms with their own NCIt codes. SDTMIG v3.4 CDISC Notes: 'Further description of the test performed in producing the MI result. This would be used to represent specific attributes, such as intensity score or percentage of cells displaying presence of the biomarker or compound.' In COSMoS MITSTDTL is the only assigned value that separates the DSSs of one BC (Allred proportion positive score, staining intensity score and total score, for the estrogen and for the progesterone receptor); all are integer without units, so scale does not separate them. Two readings: the test detail narrows what is measured (component), or it names the kind of quantity reported (a property, in LOINC's terms). Both keep the DSSs apart, unlike ISTSTDTL, where the score systems go with a change of scale. The key has no property part, so it is carried as component. Quoted in SDTMIG_Statements.xlsx: MI-A2, MITSTDTL-Notes.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7: two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT. Quoted in SDTMIG_Statements.xlsx: ISBDAGNT-Notes, IS-A7, IS-A7a, IS-A7b.</t>
+          <t>COSMoS and SDTM v2.0/SDTMIG v3.4: predicate IS_ATTRIBUTE_FOR, "is the substance bound to the analyte in", codelists ISBDAGT and MICROORG. Fan-out axis binding agent and key part component agree (Key_Compare in Domain_Behaviour). IS DSSs pin no LOINC codes. SDTM v2.0 and SDTMIG v3.4: Variable Qualifier of --TESTCD. SDTMIG v3.4 IS Assumption 7: two codelists (MICROORG, ISBDAGT); the CT Rules for Immunogenicity Tests say which to use. SDTMIG v3.4 CDISC Notes and SDTM v2.0 --BDAGNT: 'the combination of ISTEST and ISBDAGNT should describe the entity or the analyte being measured, without the need for additional variables'; 'not a method qualifier'. Assumption 7a: for antidrug antibody tests the binding agent is the study therapy name, not controlled by CDISC; sponsors extend ISBDAGT. Quoted in SDTMIG_Statements.xlsx: ISBDAGNT-Notes, IS-A7, IS-A7a, IS-A7b.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rule (decided 2026-10-06): result scale is treated as distinguishing an observable, on the standards' own grounds: DSSs of one BC differ by scale, and LOINC has scale as an axis. No claim that it is clinically right. Disagreement: the fan-out reads units present or absent; the key reads the --ORRES data type (Key_Compare). COSMoS publishes result scale per BC, not per DSS (Scale_Units). The rule does not settle which per-DSS reading is right.</t>
+          <t>Rule (decided 2026-10-06): result scale is treated as distinguishing an observable, on the standards' own grounds: DSSs of one BC differ by scale, and LOINC has scale as an axis. No claim that it is clinically right. Disagreement: the fan-out reads units present or absent; the key reads the --ORRES data type (Key_Compare in Domain_Behaviour). COSMoS publishes result scale per BC, not per DSS (Scale_Units in Domain_Behaviour). The rule does not settle which per-DSS reading is right.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing). Quoted in SDTMIG_Statements.xlsx: GF-A8, GFANMETH-Notes.</t>
+          <t>COSMoS: predicate SPECIFIES, "is the method of secondary analysis of results in", DEC Analysis Method, codelist GFANMET. Not DEC Test Method, so not the test method; the key reads --METHOD only (Key_Compare in Domain_Behaviour: method, fan-out only). No source says whether the analysis method is part of the observable. SDTMIG v3.4: Record Qualifier, 'the method of secondary processing performed by the dry lab to yield the result'. SDTMIG v3.4 GF Assumption 8 confines GFMETHOD to wet lab techniques; the IG note puts GFANMETH in the dry lab (secondary processing). Quoted in SDTMIG_Statements.xlsx: GF-A8, GFANMETH-Notes.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class). No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier.</t>
+          <t>COSMoS: predicate GROUPS, "groups values in"; DEC not stated. No codelist; values without NCIt code. LBCAT and LOINC class are different groupings (LBCAT_LOINC_Class in Domain_Behaviour). No source says whether category changes the observation. SDTM v2.0 and SDTMIG v3.4: Grouping Qualifier.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property. SDTMIG v3.4 QS Assumption 8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'; supplemental qualifiers may be used if needed. COSMoS assigns QSEVAL = CAREGIVER on the DSSs of TTS ACCEPTABILITY SURVEY - LZZT. Quoted in SDTMIG_Statements.xlsx: QS-A8.</t>
+          <t>COSMoS assigns QSEVAL = CAREGIVER on some DSSs, no value on the rest (Rater_COSMoS_EVAL in Domain_Behaviour); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence in Domain_Behaviour) and, for CC only, in the SDTM CT domain definition. No source ties the rater to the instrument as a property. SDTMIG v3.4 QS Assumption 8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'; supplemental qualifiers may be used if needed. COSMoS assigns QSEVAL = CAREGIVER on the DSSs of TTS ACCEPTABILITY SURVEY - LZZT. Quoted in SDTMIG_Statements.xlsx: QS-A8.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7: RSEVALID with RSEVAL gives detail of who provides the assessment. COSMoS assigns RSEVAL = INVESTIGATOR on Child-Pugh Classification DSSs (RSCAT codelist CCCAT, a clinical classification); the value list INVESTIGATOR;INDEPENDENT ASSESSOR is on oncology response DSSs (ONCRSCAT), and INVESTIGATOR;DERMATOLOGIST on PASI (CCCAT). The RS Clinical Classifications Use Case Assumptions (p338) carry the QRS assumption also quoted as QS-A8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'. Quoted in SDTMIG_Statements.xlsx: RS-DR-A7, QS-A8 (the RS copy cannot be selected; see its ReadMe).</t>
+          <t>COSMoS assigns RSEVAL = INVESTIGATOR on some DSSs, value list only on others (Rater_COSMoS_EVAL in Domain_Behaviour); SDTM CT codelist EVAL. A rater is also stated in NCIt definition prose (Rater_Evidence in Domain_Behaviour). No source ties the rater to the instrument as a property. SDTMIG v3.4 RS disease response Assumption 7: RSEVALID with RSEVAL gives detail of who provides the assessment. COSMoS assigns RSEVAL = INVESTIGATOR on Child-Pugh Classification DSSs (RSCAT codelist CCCAT, a clinical classification); the value list INVESTIGATOR;INDEPENDENT ASSESSOR is on oncology response DSSs (ONCRSCAT), and INVESTIGATOR;DERMATOLOGIST on PASI (CCCAT). The RS Clinical Classifications Use Case Assumptions (p338) carry the QRS assumption also quoted as QS-A8: '--EVAL and --EVALID must not be used to model QRS data in SDTM'. Quoted in SDTMIG_Statements.xlsx: RS-DR-A7, QS-A8 (the RS copy cannot be selected; see its ReadMe).</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8: LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2). Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
+          <t>COSMoS: LBFAST is a value list (N;Y), never assigned, so it never separates sibling DSSs and is not in Variable_Evidence. LOINC (Subject_State in COSMoS_Observable_LOINC_Check): fasting-free and fasting-qualified glucose codes side by side (component Glucose^post CFst, class CHAL). LOINC offers fasting as a refinement, not as a requirement; no source says whether fasting is part of the observable. SDTM v2.0 and SDTMIG v3.4: Record Qualifier, like --SPEC and --METHOD; no published role separates subject state from identifying qualifiers. SDTMIG v3.4 LB Assumption 8: LBFAST is among 'the aspects of a test that are associated with a LOINC code', 'only required to be populated when necessary to provide a semantically meaningful distinction between records with different LBLOINC values'. COSMoS, LOINC and the IG agree that subject state is an optional refinement; none says it is always or never part of the observable (decided 2026-10-08: open, the conditional reading carried into Phase 2). Quoted in SDTMIG_Statements.xlsx: LB-A8.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Interpretation_Context: COSMoS_Use = always assigned in QS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+          <t>Interpretation_Context in Domain_Behaviour: COSMoS_Use = always assigned in QS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+          <t>Interpretation_Context in Domain_Behaviour: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Interpretation_Context: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
+          <t>Interpretation_Context in Domain_Behaviour: COSMoS_Use = always assigned in RS. SDTM v2.0 role Timing; SDTMIG v3.4 Core Perm. No source states whether the evaluation interval is part of what is observed or only context for reading the result. COSMoS fixing it on every DSS that carries it is consistent with the first. Candidate for the instrument observable.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
